--- a/data/trans_orig/AIRE_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023</t>
+          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,62 +878,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2277</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>8754</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2277</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>7383</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1129</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3579</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>631</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3171</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3214</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3652</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -1182,97 +1182,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1129</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>864</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>374</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9978</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -1408,97 +1408,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2164</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2559</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>604</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16915</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14434</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26750</t>
+          <t>26527</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>15585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>13019</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29870</t>
+          <t>29153</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39438</t>
+          <t>39356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>212282</t>
+          <t>211516</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>231471</t>
+          <t>231312</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>332637</t>
+          <t>332803</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>351810</t>
+          <t>351673</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>550809</t>
+          <t>552718</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>578161</t>
+          <t>579412</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>12458</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>17928</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25633</t>
+          <t>23821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30442</t>
+          <t>29365</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>10762</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11428</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35972</t>
+          <t>38745</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -2429,97 +2429,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1552</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>362</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>17414</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>12385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28417</t>
+          <t>30309</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>15539</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14191</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>24125</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19632</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53799</t>
+          <t>50365</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>21349</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>167800</t>
+          <t>202470</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51773</t>
+          <t>51061</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>230359</t>
+          <t>193356</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37404</t>
+          <t>36327</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24162</t>
+          <t>23559</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53035</t>
+          <t>52042</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52145</t>
+          <t>52726</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>105647</t>
+          <t>104094</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33292</t>
+          <t>30346</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71209</t>
+          <t>72202</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92030</t>
+          <t>93590</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>161592</t>
+          <t>160063</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>92027</t>
+          <t>89961</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>131473</t>
+          <t>130086</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>67855</t>
+          <t>66180</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>146594</t>
+          <t>148280</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>160565</t>
+          <t>164349</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>262477</t>
+          <t>259357</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>761390</t>
+          <t>764648</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>832746</t>
+          <t>832546</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>848303</t>
+          <t>843569</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1036849</t>
+          <t>1036567</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1637570</t>
+          <t>1639704</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1865030</t>
+          <t>1874468</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3676,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>14854</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>470</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8640</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>16657</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>26424</t>
+          <t>26200</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -3902,82 +3902,82 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1786</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3373</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>659</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>3567</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4015,12 +4015,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8625</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>335</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -4128,97 +4128,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1490</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1786</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5283</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>1490</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>1491</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>5368</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>4596</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>1491</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>4699</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>23043</t>
+          <t>22753</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>9823</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>23594</t>
+          <t>24791</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>29677</t>
+          <t>30807</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>19450</t>
+          <t>19185</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>24833</t>
+          <t>25744</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4693,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>31589</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>24324</t>
+          <t>23918</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>25494</t>
+          <t>25405</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>48488</t>
+          <t>48624</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4806,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>56190</t>
+          <t>56767</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>85799</t>
+          <t>86746</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>33778</t>
+          <t>33221</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>52501</t>
+          <t>52671</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>95720</t>
+          <t>97436</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>130877</t>
+          <t>131761</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>176181</t>
+          <t>174240</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>214707</t>
+          <t>214232</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>201053</t>
+          <t>201123</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>229295</t>
+          <t>230016</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>386819</t>
+          <t>387977</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>436775</t>
+          <t>432988</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>66,98%</t>
         </is>
       </c>
     </row>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>20853</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>21632</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>36749</t>
+          <t>36022</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -5262,12 +5262,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>13963</t>
+          <t>14147</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>39324</t>
+          <t>40505</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>23886</t>
+          <t>23298</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>26968</t>
+          <t>27164</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>57204</t>
+          <t>55458</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -5375,97 +5375,97 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="R45" s="2" t="inlineStr">
         <is>
           <t>659</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="S45" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>3393</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>2835</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>0,02%</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>3265</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>322</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>15094</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,74 +5616,74 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>9085</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>8863</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>9511</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>1483</t>
-        </is>
-      </c>
-      <c r="T47" s="2" t="inlineStr">
-        <is>
-          <t>9844</t>
-        </is>
-      </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
           <t>0,04%</t>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>29725</t>
+          <t>31432</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>11607</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>28512</t>
+          <t>27531</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>26484</t>
+          <t>26850</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>51389</t>
+          <t>50400</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>17872</t>
+          <t>18438</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>19454</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>14868</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>33103</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>29056</t>
+          <t>27218</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>64300</t>
+          <t>64920</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>40856</t>
+          <t>40132</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>227443</t>
+          <t>202866</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>81070</t>
+          <t>78360</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>262368</t>
+          <t>245702</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6053,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>25271</t>
+          <t>24670</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>50776</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>27763</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>41713</t>
+          <t>40793</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>76057</t>
+          <t>73447</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>76695</t>
+          <t>78358</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>130683</t>
+          <t>132377</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>55113</t>
+          <t>56697</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>98771</t>
+          <t>99282</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>142705</t>
+          <t>144752</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>214095</t>
+          <t>220439</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>168259</t>
+          <t>166701</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>220528</t>
+          <t>218376</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>124981</t>
+          <t>124688</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>208876</t>
+          <t>211468</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>301660</t>
+          <t>298323</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>412114</t>
+          <t>410313</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -6392,12 +6392,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1175781</t>
+          <t>1170933</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1255903</t>
+          <t>1258137</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1398745</t>
+          <t>1398105</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1608013</t>
+          <t>1612956</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>2614408</t>
+          <t>2606508</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2841450</t>
+          <t>2862811</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Estudios-trans_orig.xlsx
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,22 +795,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>707</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>707</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,22 +1325,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>401</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10572</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>354</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>354</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -1516,32 +1516,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1551,32 +1551,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,22 +1586,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1629,22 +1629,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17214</t>
+          <t>21237</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>15012</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26527</t>
+          <t>33179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29153</t>
+          <t>31738</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>28675</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39356</t>
+          <t>42080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -1968,32 +1968,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>223266</t>
+          <t>255798</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>211516</t>
+          <t>243177</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>231312</t>
+          <t>266210</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2003,32 +2003,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>343313</t>
+          <t>376937</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>332803</t>
+          <t>365730</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>351673</t>
+          <t>386642</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2038,27 +2038,27 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>566579</t>
+          <t>632734</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>552718</t>
+          <t>616354</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579412</t>
+          <t>646835</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>255267</t>
+          <t>292160</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>255267</t>
+          <t>292160</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>255267</t>
+          <t>292160</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,17 +2116,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>381214</t>
+          <t>418450</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>381214</t>
+          <t>418450</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>381214</t>
+          <t>418450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>636481</t>
+          <t>710610</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>636481</t>
+          <t>710610</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>636481</t>
+          <t>710610</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2198,22 +2198,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23821</t>
+          <t>25222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>16038</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29365</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>11487</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>19555</t>
+          <t>22229</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>13272</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38745</t>
+          <t>38833</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,44 +2562,44 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5633</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5853</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -2607,32 +2607,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -2685,32 +2685,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2460</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -2763,32 +2763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>17575</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,32 +2798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>17617</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>19466</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30309</t>
+          <t>29913</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -2876,32 +2876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>13421</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24125</t>
+          <t>24403</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31287</t>
+          <t>34041</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18363</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50365</t>
+          <t>54076</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>60664</t>
+          <t>32111</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>202470</t>
+          <t>46155</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>91951</t>
+          <t>66153</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51061</t>
+          <t>47070</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>193356</t>
+          <t>92374</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>22813</t>
+          <t>23175</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>13535</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>37794</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13181</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>35994</t>
+          <t>38525</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23559</t>
+          <t>26712</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52042</t>
+          <t>54261</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -3215,32 +3215,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>73154</t>
+          <t>74070</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52726</t>
+          <t>53063</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>104094</t>
+          <t>99884</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3250,32 +3250,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>54146</t>
+          <t>61423</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>48968</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72202</t>
+          <t>76644</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>127300</t>
+          <t>135493</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>93590</t>
+          <t>111510</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>160063</t>
+          <t>166326</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -3328,32 +3328,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>110113</t>
+          <t>117606</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>89961</t>
+          <t>99130</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>130086</t>
+          <t>138783</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3363,32 +3363,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>115704</t>
+          <t>125566</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>66180</t>
+          <t>109249</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>148280</t>
+          <t>147160</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3398,32 +3398,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>225817</t>
+          <t>243173</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>164349</t>
+          <t>214317</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>259357</t>
+          <t>270521</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -3441,32 +3441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>799568</t>
+          <t>871069</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>764648</t>
+          <t>836619</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>832546</t>
+          <t>904256</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3476,32 +3476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>924661</t>
+          <t>801798</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>843569</t>
+          <t>775254</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1036567</t>
+          <t>825941</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3511,32 +3511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1724229</t>
+          <t>1672868</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1639704</t>
+          <t>1625604</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1874468</t>
+          <t>1713236</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>76,74%</t>
         </is>
       </c>
     </row>
@@ -3554,17 +3554,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1075088</t>
+          <t>1160277</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1075088</t>
+          <t>1160277</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1075088</t>
+          <t>1160277</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1202013</t>
+          <t>1072269</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1202013</t>
+          <t>1072269</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1202013</t>
+          <t>1072269</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,17 +3624,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2277101</t>
+          <t>2232547</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2277101</t>
+          <t>2232547</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2277101</t>
+          <t>2232547</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3671,27 +3671,27 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14854</t>
+          <t>15895</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3706,32 +3706,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>476</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3741,32 +3741,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -3784,27 +3784,27 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14133</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3819,32 +3819,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9756</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16657</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3854,32 +3854,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10691</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>26200</t>
+          <t>27923</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -4010,32 +4010,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>11643</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -4236,32 +4236,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13456</t>
+          <t>15751</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4271,32 +4271,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>7255</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>13089</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>22753</t>
+          <t>24564</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>14889</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -4462,32 +4462,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4497,32 +4497,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>14084</t>
+          <t>14894</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>24791</t>
+          <t>25126</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>22052</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>14578</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>30807</t>
+          <t>34312</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -4575,32 +4575,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>19185</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4610,32 +4610,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>10655</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>17327</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>25744</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4688,32 +4688,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>18173</t>
+          <t>20320</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>30412</t>
+          <t>34754</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4723,32 +4723,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>17227</t>
+          <t>20719</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>14739</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>23918</t>
+          <t>28341</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4758,32 +4758,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>41038</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>25405</t>
+          <t>30978</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>48624</t>
+          <t>55139</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -4801,32 +4801,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>70881</t>
+          <t>77086</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>56767</t>
+          <t>62584</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>86746</t>
+          <t>92480</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>42512</t>
+          <t>45874</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>33221</t>
+          <t>36811</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>52671</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>113393</t>
+          <t>122959</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>97436</t>
+          <t>105858</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>131761</t>
+          <t>143009</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -4914,32 +4914,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>194245</t>
+          <t>202378</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>174240</t>
+          <t>183139</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>214232</t>
+          <t>220626</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4949,32 +4949,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>215692</t>
+          <t>245962</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>201123</t>
+          <t>228942</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>230016</t>
+          <t>260130</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4984,32 +4984,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>409938</t>
+          <t>448340</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>387977</t>
+          <t>423404</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>432988</t>
+          <t>473603</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,68%</t>
         </is>
       </c>
     </row>
@@ -5027,17 +5027,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>323814</t>
+          <t>346652</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>323814</t>
+          <t>346652</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>323814</t>
+          <t>346652</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5062,17 +5062,17 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>322646</t>
+          <t>363628</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>322646</t>
+          <t>363628</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>322646</t>
+          <t>363628</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5097,17 +5097,17 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>646461</t>
+          <t>710280</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>646461</t>
+          <t>710280</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>646461</t>
+          <t>710280</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5144,102 +5144,102 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>12294</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>6984</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>22433</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>25600</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>15982</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>38899</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>11310</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>5994</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>21632</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>22967</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>14177</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>36022</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -5257,69 +5257,69 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>23657</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>40505</t>
+          <t>42181</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>17446</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>11063</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>26446</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>15035</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>8252</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>23298</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>43</t>
@@ -5327,32 +5327,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>27164</t>
+          <t>29979</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>55458</t>
+          <t>60435</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5483,32 +5483,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>12859</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>15381</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -5631,22 +5631,22 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,17 +5666,17 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>9154</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>31432</t>
+          <t>31764</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5744,32 +5744,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>20531</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>11607</t>
+          <t>14212</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>27531</t>
+          <t>30278</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>40358</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>26850</t>
+          <t>29895</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>50400</t>
+          <t>53828</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -5822,102 +5822,102 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>12601</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>7225</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>19945</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>22948</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>14695</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>32685</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>12249</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>6817</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>19854</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>22709</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>14021</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>34271</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5935,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>46656</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>27218</t>
+          <t>31278</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>64920</t>
+          <t>68427</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5970,32 +5970,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>51646</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>40132</t>
+          <t>39221</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>202866</t>
+          <t>68157</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>120940</t>
+          <t>98302</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>78360</t>
+          <t>79355</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>245702</t>
+          <t>127205</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -6048,32 +6048,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>37958</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>24670</t>
+          <t>26204</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>50776</t>
+          <t>52900</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6083,32 +6083,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>21671</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>28253</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6118,32 +6118,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>55713</t>
+          <t>59629</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>40793</t>
+          <t>44815</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>73447</t>
+          <t>77422</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -6161,32 +6161,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>100839</t>
+          <t>106492</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>78358</t>
+          <t>83381</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>132377</t>
+          <t>135800</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6196,32 +6196,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>92052</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>56697</t>
+          <t>77229</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>99282</t>
+          <t>109516</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6231,32 +6231,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>181318</t>
+          <t>198544</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>144752</t>
+          <t>171983</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>220439</t>
+          <t>231766</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -6274,32 +6274,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>190204</t>
+          <t>204442</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>166701</t>
+          <t>178227</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>218376</t>
+          <t>231552</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6309,32 +6309,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>177680</t>
+          <t>192669</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>124688</t>
+          <t>170435</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>211468</t>
+          <t>218241</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6344,32 +6344,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>367884</t>
+          <t>397111</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>298323</t>
+          <t>364597</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>410313</t>
+          <t>432072</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -6387,32 +6387,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1217080</t>
+          <t>1329244</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1170933</t>
+          <t>1287482</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1258137</t>
+          <t>1369098</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6422,32 +6422,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>1483665</t>
+          <t>1424698</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1398105</t>
+          <t>1390901</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1612956</t>
+          <t>1454035</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6457,32 +6457,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>2700745</t>
+          <t>2753942</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>2606508</t>
+          <t>2702323</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2862811</t>
+          <t>2802951</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -6500,17 +6500,17 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>1654169</t>
+          <t>1799089</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1654169</t>
+          <t>1799089</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1654169</t>
+          <t>1799089</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6535,17 +6535,17 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>1905873</t>
+          <t>1854348</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1905873</t>
+          <t>1854348</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1905873</t>
+          <t>1854348</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6570,17 +6570,17 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>3560042</t>
+          <t>3653437</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3560042</t>
+          <t>3653437</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3560042</t>
+          <t>3653437</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">

--- a/data/trans_orig/AIRE_1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
